--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Text.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Text.xlsx
@@ -1,16 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
 <workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
-  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="10608"/>
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="5" rupBuild="29822"/>
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="/Users/tanghai/Documents/WOW/Packages/cn.etetet.wow/Luban/Config/Datas/"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\05ET\MatchTest\ETGame\Packages\cn.etetet.statesync\Luban\Config\Datas\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{244C8C56-A0D8-CA45-862A-26A3BDC991C9}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{04136B8F-04F4-40CA-8A15-F156CF648122}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="0" yWindow="0" windowWidth="38400" windowHeight="20560" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="0" yWindow="0" windowWidth="28830" windowHeight="7800" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="text" sheetId="1" r:id="rId1"/>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="15" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,30 @@
   </si>
   <si>
     <t>英文</t>
+  </si>
+  <si>
+    <t>MapPoi_Evacuation_Self</t>
+  </si>
+  <si>
+    <t>我方撤离点</t>
+  </si>
+  <si>
+    <t>MapPoi_HighContainer</t>
+  </si>
+  <si>
+    <t>高级容器</t>
+  </si>
+  <si>
+    <t>MapPoi_BossSpawn</t>
+  </si>
+  <si>
+    <t>Boss刷新点</t>
+  </si>
+  <si>
+    <t>MapPoi_MissionTask</t>
+  </si>
+  <si>
+    <t>任务点</t>
   </si>
 </sst>
 </file>
@@ -412,17 +436,17 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
-  <dimension ref="A1:E3"/>
-  <sheetFormatPr baseColWidth="10" defaultColWidth="9" defaultRowHeight="15"/>
+  <dimension ref="A1:E7"/>
+  <sheetFormatPr defaultColWidth="9" defaultRowHeight="14.25"/>
   <cols>
     <col min="1" max="1" width="12.5" customWidth="1"/>
-    <col min="2" max="2" width="15.83203125" customWidth="1"/>
+    <col min="2" max="2" width="15.875" customWidth="1"/>
     <col min="3" max="3" width="36.5" customWidth="1"/>
     <col min="4" max="4" width="28" customWidth="1"/>
-    <col min="5" max="5" width="20.6640625" customWidth="1"/>
+    <col min="5" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16">
+    <row r="1" spans="1:5" ht="16.5">
       <c r="A1" t="s">
         <v>0</v>
       </c>
@@ -439,7 +463,7 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16">
+    <row r="2" spans="1:5" ht="16.5">
       <c r="A2" t="s">
         <v>5</v>
       </c>
@@ -456,7 +480,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17" customHeight="1">
+    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
       <c r="A3" t="s">
         <v>8</v>
       </c>
@@ -471,6 +495,50 @@
       </c>
       <c r="E3" s="1" t="s">
         <v>11</v>
+      </c>
+    </row>
+    <row r="4" spans="1:5">
+      <c r="A4">
+        <v>38008</v>
+      </c>
+      <c r="B4" t="s">
+        <v>12</v>
+      </c>
+      <c r="C4" t="s">
+        <v>13</v>
+      </c>
+    </row>
+    <row r="5" spans="1:5">
+      <c r="A5">
+        <v>38009</v>
+      </c>
+      <c r="B5" t="s">
+        <v>14</v>
+      </c>
+      <c r="C5" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="6" spans="1:5">
+      <c r="A6">
+        <v>38010</v>
+      </c>
+      <c r="B6" t="s">
+        <v>16</v>
+      </c>
+      <c r="C6" t="s">
+        <v>17</v>
+      </c>
+    </row>
+    <row r="7" spans="1:5">
+      <c r="A7">
+        <v>38011</v>
+      </c>
+      <c r="B7" t="s">
+        <v>18</v>
+      </c>
+      <c r="C7" t="s">
+        <v>19</v>
       </c>
     </row>
   </sheetData>

--- a/Packages/cn.etetet.statesync/Luban/Config/Datas/Text.xlsx
+++ b/Packages/cn.etetet.statesync/Luban/Config/Datas/Text.xlsx
@@ -15,7 +15,7 @@
   <sheets>
     <sheet name="text" sheetId="1" r:id="rId1"/>
   </sheets>
-  <calcPr calcId="191029"/>
+  <calcPr calcId="191029" fullCalcOnLoad="1" fullPrecision="1"/>
   <extLst>
     <ext xmlns:xcalcf="http://schemas.microsoft.com/office/spreadsheetml/2018/calcfeatures" uri="{B58B0392-4F1F-4190-BB64-5DF3571DCE5F}">
       <xcalcf:calcFeatures>
@@ -33,7 +33,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="20">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="21" uniqueCount="21">
   <si>
     <t>##var</t>
   </si>
@@ -69,6 +69,9 @@
   </si>
   <si>
     <t>英文</t>
+  </si>
+  <si>
+    <t/>
   </si>
   <si>
     <t>MapPoi_Evacuation_Self</t>
@@ -99,7 +102,8 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="4">
+  <numFmts count="0"/>
+  <fonts count="3">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -117,13 +121,6 @@
     <font>
       <sz val="11"/>
       <color theme="1"/>
-      <name val="等线"/>
-      <family val="4"/>
-      <charset val="134"/>
-      <scheme val="minor"/>
-    </font>
-    <font>
-      <sz val="9"/>
       <name val="等线"/>
       <family val="4"/>
       <charset val="134"/>
@@ -155,11 +152,11 @@
   </borders>
   <cellStyleXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="0"/>
+    <xf numFmtId="0" fontId="2" applyFont="1" fillId="0" borderId="0"/>
   </cellStyleXfs>
   <cellXfs count="2">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="1" applyFont="1" applyFill="1"/>
+    <xf numFmtId="0" fontId="1" applyFont="1" fillId="2" applyFill="1" borderId="0" xfId="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -446,8 +443,8 @@
     <col min="5" max="5" width="20.625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="16.5">
-      <c r="A1" t="s">
+    <row r="1" ht="16.5">
+      <c r="A1" s="0" t="s">
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
@@ -463,8 +460,8 @@
         <v>4</v>
       </c>
     </row>
-    <row r="2" spans="1:5" ht="16.5">
-      <c r="A2" t="s">
+    <row r="2" ht="16.5">
+      <c r="A2" s="0" t="s">
         <v>5</v>
       </c>
       <c r="B2" s="1" t="s">
@@ -480,8 +477,8 @@
         <v>7</v>
       </c>
     </row>
-    <row r="3" spans="1:5" ht="17.100000000000001" customHeight="1">
-      <c r="A3" t="s">
+    <row r="3" ht="17.1" customHeight="1">
+      <c r="A3" s="0" t="s">
         <v>8</v>
       </c>
       <c r="B3" s="1" t="s">
@@ -497,53 +494,83 @@
         <v>11</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
-      <c r="A4">
+    <row r="4">
+      <c r="A4" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B4" s="0">
         <v>38008</v>
       </c>
-      <c r="B4" t="s">
-        <v>12</v>
-      </c>
-      <c r="C4" t="s">
+      <c r="C4" s="0" t="s">
         <v>13</v>
       </c>
-    </row>
-    <row r="5" spans="1:5">
-      <c r="A5">
+      <c r="D4" s="0" t="s">
+        <v>14</v>
+      </c>
+      <c r="E4" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B5" s="0">
         <v>38009</v>
       </c>
-      <c r="B5" t="s">
-        <v>14</v>
-      </c>
-      <c r="C5" t="s">
+      <c r="C5" s="0" t="s">
         <v>15</v>
       </c>
-    </row>
-    <row r="6" spans="1:5">
-      <c r="A6">
+      <c r="D5" s="0" t="s">
+        <v>16</v>
+      </c>
+      <c r="E5" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B6" s="0">
         <v>38010</v>
       </c>
-      <c r="B6" t="s">
-        <v>16</v>
-      </c>
-      <c r="C6" t="s">
+      <c r="C6" s="0" t="s">
         <v>17</v>
       </c>
-    </row>
-    <row r="7" spans="1:5">
-      <c r="A7">
+      <c r="D6" s="0" t="s">
+        <v>18</v>
+      </c>
+      <c r="E6" s="0" t="s">
+        <v>12</v>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" s="0" t="s">
+        <v>12</v>
+      </c>
+      <c r="B7" s="0">
         <v>38011</v>
       </c>
-      <c r="B7" t="s">
-        <v>18</v>
-      </c>
-      <c r="C7" t="s">
+      <c r="C7" s="0" t="s">
         <v>19</v>
+      </c>
+      <c r="D7" s="0" t="s">
+        <v>20</v>
+      </c>
+      <c r="E7" s="0" t="s">
+        <v>12</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="3" type="noConversion"/>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait"/>
+  <headerFooter/>
 </worksheet>
+</file>
+
+<file path=EPPlusLicense.txt>This workbook was created with the EPPlus library, licensed to ETET under the Polyform Noncommercial license, see https://polyformproject.org/licenses/noncommercial/1.0.0
+For more information about EPPlus, see https://epplussoftware.com/
+
 </file>